--- a/test/kernberk_Data/StreamingAssets/kernberk_sheet.xlsx
+++ b/test/kernberk_Data/StreamingAssets/kernberk_sheet.xlsx
@@ -5,13 +5,15 @@
   <sheets>
     <sheet state="visible" name="시트1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'시트1'!$O$2:$O$195</definedName>
+  </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="210">
   <si>
     <t>sceneName</t>
   </si>
@@ -37,6 +39,9 @@
     <t>sceneFadeType</t>
   </si>
   <si>
+    <t>nextScene</t>
+  </si>
+  <si>
     <t>sfx</t>
   </si>
   <si>
@@ -58,125 +63,367 @@
     <t>scene01</t>
   </si>
   <si>
+    <t>SCENE_START</t>
+  </si>
+  <si>
+    <t>ash</t>
+  </si>
+  <si>
+    <t>scene1-1</t>
+  </si>
+  <si>
+    <t>사랑하는 어머니께.</t>
+  </si>
+  <si>
+    <t>안녕하십니까 어머니. 아들입니다.</t>
+  </si>
+  <si>
+    <t>저는 아니나 다를까 '케런베르크' 로 향하는 마차 안 입니다.</t>
+  </si>
+  <si>
+    <t>수도에서 흔하디 흔한 경비병 중 한 명으로 근무하던 저였지만, 이런 혼란스러운 전쟁통에 역시 파병을 피할수는 없었나봅니다.</t>
+  </si>
+  <si>
+    <t>뭐 그래도, 그저 그런 사람으로써 역사에 이름도 남겨보지 못하고 허무한 죽음을 맞이하는 것 보다야</t>
+  </si>
+  <si>
+    <t>나라를 위해 한 몸 바치다가 맞이하는 죽음이 훨씬 훌륭할거라고 생각합니다.</t>
+  </si>
+  <si>
+    <t>먼 미래의 교과서에 이름 한 글자 정도는 남길 수 있지 않을까요?</t>
+  </si>
+  <si>
+    <t>어머니는 항상 이런 저를 다그치며, 너무 나서지 말아라 쥐 죽은듯 조용히 평범한 삶을 살으라 하셨지만,</t>
+  </si>
+  <si>
+    <t>어짜피 저는 평범하게 살다가 평범하게 죽게 되지는 못할 운명이었나 봅니다.</t>
+  </si>
+  <si>
+    <t>어찌되었든 미래를 저주하고 있을 수 만은 없으니,</t>
+  </si>
+  <si>
+    <t>전쟁에 아무짝에도 도움이 되지 않는 저일테지만 그래도 왕국을 위해 이 한 몸 헌신하고 바칠 생각입니다.</t>
+  </si>
+  <si>
+    <t>운이 좋으면 다시 찾아뵙도록 하겠습니다.</t>
+  </si>
+  <si>
+    <t>아들 드림</t>
+  </si>
+  <si>
+    <t>조용히 마음속의 편지지를 닫았다.</t>
+  </si>
+  <si>
+    <t>마차 주변을 둘러보면 썩 좋지 않은 표정들의 병사들로 가득했다.</t>
+  </si>
+  <si>
+    <t>우리가 향하는 곳은 "케런베르크" 왕국과 지금 전쟁을 치르고 있는 인간이 아닌 존재 "다인" 이라는 녀석들과 만날 수 있는 최전선에 위치한 곳이다.</t>
+  </si>
+  <si>
+    <t>녀석들이 어떤 녀석들인지, 어디서부터 온 녀석들인지는 알려져있지 않다.</t>
+  </si>
+  <si>
+    <t>다만 확실한건 녀석들은 분명히 이 거대한 왕국을 적으로 두고, 우리를 위협하고 있다는 것이다.</t>
+  </si>
+  <si>
+    <t>이미 "다인" 녀석들에 의해 왕국의 많은 성들이 무너졌고, 1/3에 가까운 영토를 잃었다. 그 만큼 많은 사람도 죽었다.</t>
+  </si>
+  <si>
+    <t>그 만큼 강력한 녀석들을 우리같은 일반 병사들이 어떻게 상대하라는 건지 모르지만...</t>
+  </si>
+  <si>
+    <t>듣기로는 우리와 함께 왕국의 마법 기사단 학교에서도 몇명 지원병이 온다고 한다.</t>
+  </si>
+  <si>
+    <t>마법을 사용할 수 있는 병사는 굉장히 드물다.</t>
+  </si>
+  <si>
+    <t>귀족들의 전유물이나 다름없는 마법을 사용하는, 강한 귀족들로 이루어진 마법 기사단이 왕국에는 존재하지만 그 수는 굉장히 한정되어있고, 이렇게 큰 전쟁에서는 수가 한창 부족한 것이다.</t>
+  </si>
+  <si>
+    <t>그러다보니 자연스레 아직 훈련이 덜 된 기사단 학교에서도 몇명씩 이렇게 차출되어서 훌륭한 전력이 된다는 것은 이해는 하지만...</t>
+  </si>
+  <si>
+    <t>어린 나이의 학생들에게 전장으로 향하라고 하는것은 썩 마음에 들지는 않는 것이었다.</t>
+  </si>
+  <si>
+    <t>하지만 그런 학생들이 우리같이 아무런 능력이 없는 일반 병사들에 비해서는 훨씬 전력이 되는 것이겠지...</t>
+  </si>
+  <si>
+    <t>어떻게든 그들의 도움이 되고 방패막이가 되기위해 노력하는 수 밖에 없을 것이다.</t>
+  </si>
+  <si>
+    <t>dark</t>
+  </si>
+  <si>
+    <t>...</t>
+  </si>
+  <si>
+    <t>scene1-2</t>
+  </si>
+  <si>
+    <t>마차를 탄 지 수 시간이 지났고, 어느새 저녁 무렵의 어스름이 하늘을 뒤덮기 시작했다.</t>
+  </si>
+  <si>
+    <t>케런베르크까지는 앞으로도 꼬박 하루는 더 달려야 도착할 수 있는 거리였다.</t>
+  </si>
+  <si>
+    <t>어둠 속에서 이동하는 건 위험하기에, 근처 적당한 숲 가장자리에서 야영을 준비하게 되었다.</t>
+  </si>
+  <si>
+    <t>스무 명 남짓의 병사들이 어수선하게 움직이며 천막을 세우고, 불을 피우고 있었다.</t>
+  </si>
+  <si>
+    <t>우리 병사들은 특정한 부대 소속이 아니었다.</t>
+  </si>
+  <si>
+    <t>수도의 서로 다른 지역에서 끌려온 일반 병사들이라, 당연히 서로 친분은커녕 제대로 된 얼굴도 기억하지 못하는 오합지졸들이었다.</t>
+  </si>
+  <si>
+    <t>그나마 몇몇 병사들끼리는 예전에 수도 근처의 경비 근무에서 만난 적이 있는지 가끔씩 짧게 대화를 나누는 모습이 보이긴 했지만, 대부분은 침묵한 채 어색하고 무거운 공기만을 뿜어내고 있었다.</t>
+  </si>
+  <si>
+    <t>그런 어색한 침묵 속에서도 눈에 띄는 인물이 한 명 있었다. "레굴루스"라고 불리는 병사였다.</t>
+  </si>
+  <si>
+    <t>귀족 집안 출신이라고 했던가.</t>
+  </si>
+  <si>
+    <t>어느 귀족가에서 태어났다고 해서 모두 마법을 쓸 수 있는 것은 아니다.</t>
+  </si>
+  <si>
+    <t>마법은 타고난 마력과 재능에 따라 결정되기에, 능력 없는 귀족들도 흔하다.</t>
+  </si>
+  <si>
+    <t>하지만 그런 귀족들은 대부분 호화로운 저택에서 부유한 삶을 보내는 걸 선택하지, 굳이 일반 병사로 자원해 위험한 최전선에 몸을 던지진 않는다.</t>
+  </si>
+  <si>
+    <t>그렇기에 레굴루스의 존재는 확실히 특별했다.</t>
+  </si>
+  <si>
+    <t>그가 어떤 각오로 여기에 왔는지는 나 같은 사람이 보아도 느낄 수 있을 정도였다.</t>
+  </si>
+  <si>
+    <t>그래서인지, 레굴루스 주변에는 마치 불빛을 향해 몰려드는 나방처럼 사람들의 무리가 형성되고 있었다.</t>
+  </si>
+  <si>
+    <t>그의 주위를 맴도는 병사들은 이제 막 형성된 무리임에도 이미 꽤나 친밀한 모습을 보이고 있었다.</t>
+  </si>
+  <si>
+    <t>나는 그런 모습이 불편했다. 아니, 불편하다는 표현보다... 소속감을 느끼고 싶지 않았다는 표현이 더 정확할 것이다. 어차피 누군가와 가까워진다고 해서 이 전장에서 무엇이 달라질까 싶기도 했으니까.</t>
+  </si>
+  <si>
+    <t>그렇게 시간을 보내고 있으니 밤의 장막이 완전히 내려앉았다.</t>
+  </si>
+  <si>
+    <t>그 무리는 잠이 오지 않는지, 불 주위에 앉아 낮은 목소리로 떠들기 시작했다.</t>
+  </si>
+  <si>
+    <t>꼭 무슨 축제라도 벌이려는 듯이 어색한 웃음소리와 술렁이는 말소리가 내 귀에 거슬렸다.</t>
+  </si>
+  <si>
+    <t>이해 못 할 바는 아니었다. 아마도 불안한 마음을 조금이나마 달래고 싶었던 거겠지.</t>
+  </si>
+  <si>
+    <t>하지만 나는 그들과 섞이고 싶은 생각이 없었기에 조용히 자리를 피해 마차로 걸음을 옮겼다.</t>
+  </si>
+  <si>
+    <t>마차 안은 예상보다 더 차갑고 서늘한 공기가 감돌았다. 밖에서 불어오는 바람이 틈새를 파고들어 몸을 조금씩 떨리게 만들었다.</t>
+  </si>
+  <si>
+    <t>그래도 천천히 몸을 웅크린 채 모포를 두툼하게 덮으니 견딜 만한 정도는 되었다.</t>
+  </si>
+  <si>
+    <t>내일이면 또 하루 종일 흔들리는 마차 위에서 시간을 보내야만 한다.</t>
+  </si>
+  <si>
+    <t>미리 체력을 조금이라도 보충해 두지 않으면 내일 케런베르크에 도착했을 때 제대로 움직일 수 있을지조차 확신할 수 없었다.</t>
+  </si>
+  <si>
+    <t>나는 그렇게 마차 구석에 몸을 웅크리고 앉아, 두 눈을 조용히 감았다. 그 불안하고 조용한 어둠 속에서, 잠은 생각보다 빨리 찾아왔다.</t>
+  </si>
+  <si>
+    <t>abgrund</t>
+  </si>
+  <si>
+    <t>그리고 깨어나는 데까지는 그리 오랜 시간이 걸리지 않았다.</t>
+  </si>
+  <si>
+    <t>코끝을 강하게 자극하는 비릿한 피 냄새.</t>
+  </si>
+  <si>
+    <t>지금까지 어떻게 이런 상황에서도 잠들 수 있었는지 믿기지 않을 정도로, 거대하고 무거운 무언가가 천천히 다가오는 소리가 들렸다.</t>
+  </si>
+  <si>
+    <t>쿵…. 쿵….</t>
+  </si>
+  <si>
+    <t>마치 지면이 울리며 갈라질 듯한 진동에 귀가 먹먹해졌다.</t>
+  </si>
+  <si>
+    <t>나는 직감적으로 무언가 잘못되었다는 것을 깨닫고 재빨리 옆에 둔 장비를 착용했다.</t>
+  </si>
+  <si>
+    <t>scene1-3</t>
+  </si>
+  <si>
+    <t>서둘러 마차 밖으로 뛰쳐나갔을 때, 내 눈에 비친 것은 지옥 그 자체였다.</t>
+  </si>
+  <si>
+    <t>참혹하게 훼손된 병사들의 시체가 여기저기 널브러져 있었다. 조금 전까지 함께 있었던 병사들 대부분이었다.</t>
+  </si>
+  <si>
+    <t>그리고 그 시체들 너머로 거대한 형상이 위협적으로 서 있었다. 인간과 비슷하지만 인간이라 하기엔 너무 거대한 그것은 쉽게 정체를 알 수 있었다.</t>
+  </si>
+  <si>
+    <t>주인공</t>
+  </si>
+  <si>
+    <t>"다인…!"</t>
+  </si>
+  <si>
+    <t>녀석은 무언가를 힘껏 집어 던졌고, 곧 이어 끔찍한 비명소리가 밤하늘을 찢었다.</t>
+  </si>
+  <si>
+    <t>사람이 그렇게도 하찮게 죽어가는 모습에 가슴이 먹먹해졌다.</t>
+  </si>
+  <si>
+    <t>그 근처에 아직 살아있는 몇몇 병사들이 있었다.</t>
+  </si>
+  <si>
+    <t>아까 본 레굴루스와 그를 따르던 병사들이었다. 그들은 절망적인 상황에서도 필사적으로 협력하여 다인을 쓰러트리려고 하고 있었다.</t>
+  </si>
+  <si>
+    <t>레굴루스</t>
+  </si>
+  <si>
+    <t>"내가 녀석의 시선을 끌겠다! 너희는 그 틈에 다리를 노려! 몸집이 크니 다리가 약점일 거다!"</t>
+  </si>
+  <si>
+    <t>레굴루스는 재빠르게 다인의 주위를 돌며 주의를 끌었다. 다인은 그 움직임에 속아 헛주먹질을 하며 점점 성급해졌다.</t>
+  </si>
+  <si>
+    <t>잠시 동안은 그의 작전이 먹히는 듯했다.</t>
+  </si>
+  <si>
+    <t>그러나 그 순간은 너무 짧았다.</t>
+  </si>
+  <si>
+    <t>쿵!!!</t>
+  </si>
+  <si>
+    <t>다인이 발을 크게 내리찍자, 지면 전체가 흔들렸다. 중심을 잃은 레굴루스가 순간적으로 휘청이며 넘어졌다.</t>
+  </si>
+  <si>
+    <t>다음 순간, 다인은 믿을 수 없는 빠른 움직임으로 그에게 다가가 그의 몸을 사정없이 내리쳤다.</t>
+  </si>
+  <si>
+    <t>레굴루스의 몸이 사람의 몸이라 믿기 힘든 각도로 꺾이며 쓰러졌다. 더 이상 그의 입에서 비명이 흘러나오지 않았다.</t>
+  </si>
+  <si>
+    <t>남은 병사들은 공포에 질려 도망치기 시작했지만, 다인이 다시 한번 발을 강하게 내리찍자 달아나던 병사들 모두가 그대로 땅에 쓰러졌고, 그들은 순식간에 다인의 손에 무참히 살해당했다.</t>
+  </si>
+  <si>
+    <t>나는 그 끔찍한 광경에 넋이 나간 채 그대로 서 있었다.</t>
+  </si>
+  <si>
+    <t>정신을 차렸을 때는 이미 주변에 살아있는 사람은 아무도 없었다. 오직 나와 다인만이 그 자리에 남아 있었다.</t>
+  </si>
+  <si>
+    <t>녀석은 홀로 서 있는 나를 발견하고 천천히 내게 한 걸음씩 다가오기 시작했다.</t>
+  </si>
+  <si>
+    <t>나는 그의 모습을 뚫어지게 쳐다보았다.</t>
+  </si>
+  <si>
+    <t>끔찍한 모습이었다. 그 이질적인 존재감은 말로 표현하기 어려웠다. 분노인지 광기인지, 이해할 수 없는 감정이 뒤섞인 표정으로 나를 바라보고 있었다.</t>
+  </si>
+  <si>
+    <t>저 녀석은 대체 무엇 때문에 저리도 분노에 차 있는 걸까?</t>
+  </si>
+  <si>
+    <t>나는 조용히 검을 쥔 손에 힘을 주었다.</t>
+  </si>
+  <si>
+    <t>어머니, 죄송하지만 약속을 지킬 수 없을 것 같아요.</t>
+  </si>
+  <si>
+    <t>못난 아들을 부디 용서해주세요.</t>
+  </si>
+  <si>
+    <t>그렇게 결의를 다지고 검을 꺼내려는 순간이었다.</t>
+  </si>
+  <si>
+    <t>tokusa</t>
+  </si>
+  <si>
+    <t>scene1-4</t>
+  </si>
+  <si>
+    <t>파지직——!</t>
+  </si>
+  <si>
+    <t>공기를 찢는 날카로운 전기 소리가 울려 퍼졌다.</t>
+  </si>
+  <si>
+    <t>순간적으로 시야가 새하얗게 번쩍였다.</t>
+  </si>
+  <si>
+    <t>그것은 하늘에서 내리꽂히는 번개처럼 순식간이었다. 번개의 형체는 빠른 속도로 내 앞을 지나쳐, 다인의 몸통 한가운데를 강력하게 강타했다.</t>
+  </si>
+  <si>
+    <t>다인은 강력한 충격에 의해 뒤로 크게 밀려나며 바닥에 무겁게 쓰러졌다.</t>
+  </si>
+  <si>
+    <t>마치 폭발이 일어난 듯 사방으로 먼지가 퍼져나갔다.</t>
+  </si>
+  <si>
+    <t>흙먼지가 걷히자, 그 번개의 정체가 서서히 모습을 드러냈다.</t>
+  </si>
+  <si>
+    <t>짧게 휘날리는 노란 머리카락. 소녀는 한 손에 검을 쥐고 있었다.</t>
+  </si>
+  <si>
+    <t>shian</t>
+  </si>
+  <si>
+    <t>LEFT_CENTER</t>
+  </si>
+  <si>
     <t>FADE_IN</t>
   </si>
   <si>
-    <t>SCENE_START</t>
-  </si>
-  <si>
-    <t>Inertia</t>
-  </si>
-  <si>
-    <t>to_kernberk</t>
-  </si>
-  <si>
-    <t>사랑하는 어머니께.</t>
-  </si>
-  <si>
-    <t>잘 지내시죠? 아들입니다.</t>
-  </si>
-  <si>
-    <t>저는 지금 케런베르크로 향하는 마차 안에 앉아있습니다.</t>
-  </si>
-  <si>
-    <t>요즘 어딘가 심상치 않더니, 역시나 ‘다인’이 다시 움직이기 시작한 모양이에요.</t>
-  </si>
-  <si>
-    <t>왕국에서 케런베르크 지원병을 선출해서, 어찌 된 영문인지 저도 그 속에 포함되었답니다.</t>
-  </si>
-  <si>
-    <t>자발적으로 간 건 아니에요. 그냥... 가만히 서 있었을 뿐인데, 어느새 마차에 실려 있더라고요. 인생이란 참 신기하죠?</t>
-  </si>
-  <si>
-    <t>어머니께서 항상 쥐 죽은 듯이 조용히 살라고 하셨었는데...</t>
-  </si>
-  <si>
-    <t>그 말씀대로 살아보려 했는데, 세상이 절 그냥 두질 않네요.</t>
-  </si>
-  <si>
-    <t>결국 이렇게, 왕국의 명령에 따라 저 무시무시한 전선으로 끌려가는 중입니다.</t>
-  </si>
-  <si>
-    <t>그래도 너무 걱정은 마세요.</t>
-  </si>
-  <si>
-    <t>왕국 군대에서 저 같은 일반병은 아주 적은 비중일 뿐이고, 대부분은 고귀하고 강하신 마법 기사단 분들이 알아서 싸워주실 거예요.</t>
-  </si>
-  <si>
-    <t>저는 어디까지나 옆에서 박수치고, 가끔 짐 들어드리는 정도의 역할이니까요.</t>
-  </si>
-  <si>
-    <t>죽지 않는 선에서, 우리 아스트렐 왕국을 위해 최선을 다할 생각입니다.</t>
-  </si>
-  <si>
-    <t>기회가 된다면, 건강하게 돌아가서 다시 어머니를 찾아 뵙도록 하겠습니다.</t>
-  </si>
-  <si>
-    <t>사랑을 담아,
-아들 드림.</t>
-  </si>
-  <si>
-    <t>... 라는 편지 한장을 쓸 종이도 펜도 없다는게 씁쓸하구만</t>
-  </si>
-  <si>
-    <t>마차에서는 어느새 우리가 향하는 케런베르크 성이 보이기 시작한다.</t>
-  </si>
-  <si>
-    <t>다른 병사들의 표정들은 썩 밝아보이지는 않는다.</t>
-  </si>
-  <si>
-    <t>사실 우리같은 일반병들은 전쟁에서 '희생' 당하는 역이다.</t>
-  </si>
-  <si>
-    <t>왕국에서 강한 마법을 사용할 수 있는 귀한 마법 기사단의 수는 아주 한정되어있다.</t>
-  </si>
-  <si>
-    <t>그렇기에 그들이 잘 싸울 수 있도록 전선의 제일 앞에서 죽는 것이 우리의 존재의의라고 할 수 있다.</t>
-  </si>
-  <si>
-    <t>아스트렐 왕국이 전쟁에서 큰 우위를 점하고있으면 혹 모를까, 다인 이라고 하는 인간이 아닌 세력은 왕국에 큰 위협을 주고 있고, 왕국은 이미 많은 성들이 함락되었다.</t>
-  </si>
-  <si>
-    <t>케런베르크도 곧 그렇게 될 예정인 곳이다.</t>
-  </si>
-  <si>
-    <t>사실상 우리는 죽으러 가고 있는 것이나 마찬가지다.</t>
-  </si>
-  <si>
-    <t>마법 기사단 분들께서는 설령 성이 함락당하더라도, 귀하신 목숨을 지켜야하니 살아서 돌아갈수도 있지만 그를 위한 시간벌이를 하는것도 우리의 몫이다.</t>
-  </si>
-  <si>
-    <t>... 아아 어머니</t>
-  </si>
-  <si>
-    <t>어머니 말씀대로 전쟁통에 왕국의 병사가 된다는 것은 미친 짓이었던 것 같아요.</t>
-  </si>
-  <si>
-    <t>그냥 왕국 내의 치안 정도를 지키는 꼬봉 정도가 될 줄 알았건만...</t>
-  </si>
-  <si>
-    <t>취업한지 1년도 안되어서 이렇게 최전선 성으로 오게될 줄은 꿈에도 몰랐군요.</t>
-  </si>
-  <si>
-    <t>역시 주위에서 엄마말 잘 들으라고 하는 말들은 괜히 그런 것이 아니군요.</t>
-  </si>
-  <si>
-    <t>그런 생각을 하고있었더니, 어느새 마차는 케런베르크로 들어가고 있는 모양이었다.</t>
-  </si>
-  <si>
-    <t>길거리에는 사람들이 거의 보이지 않는다.</t>
-  </si>
-  <si>
-    <t>마차는 성 근처 즈음에서 바로 세워진다. 앞으로 우리가 생활할 병영이다.</t>
-  </si>
-  <si>
-    <t>전쟁 중에는 즉시 출동할 일이 많기 때문에 대부분 단체 생활을 하게 된다.</t>
-  </si>
-  <si>
-    <t>생판 모르는 사람들이랑 하루종일 같이 있어야 하는 것은 좀처럼 쉬운 일은 아니다.</t>
-  </si>
-  <si>
-    <t>이게 얼마동안 계속 되는 것일지...</t>
+    <t>???</t>
+  </si>
+  <si>
+    <t>"물러나세요."</t>
+  </si>
+  <si>
+    <t>그녀의 목소리는 어린 나이답지 않게 단단하고 침착했다.</t>
+  </si>
+  <si>
+    <t>소녀의 손 주위에는 '노란색'의 마법진이 빛을 내며 천천히 회전하고 있었다. 우리를 뒤따라 온 마법학교 학생 중 한 명이라는 것을 금방 깨달았다.</t>
+  </si>
+  <si>
+    <t>다인</t>
+  </si>
+  <si>
+    <t>"쿠오오————!"</t>
+  </si>
+  <si>
+    <t>쓰러졌던 다인이 분노에 가득 찬 괴성을 지르며 다시 일어났다. 녀석은 불타듯 뜨거운 눈으로 소녀를 노려봤다.</t>
+  </si>
+  <si>
+    <t>소녀는 조용히 주변을 살폈다. 그녀의 발치 주변으로 수십 명의 병사들이 숨을 거둔 채 쓰러져 있었다.</t>
+  </si>
+  <si>
+    <t>그녀의 눈빛이 어두워졌다.</t>
+  </si>
+  <si>
+    <t>곧 그녀는 다시 한번 검을 강하게 쥐었다. 전기 마법진이 더욱 강렬하게 빛났다.</t>
+  </si>
+  <si>
+    <t>"무사히 돌아갈 수 있을 거라고 생각하지 마!!!!"</t>
   </si>
   <si>
     <t>FADE_OUT</t>
@@ -185,368 +432,224 @@
     <t>SCENE_END</t>
   </si>
   <si>
-    <t>scene02</t>
-  </si>
-  <si>
-    <t>barracks</t>
-  </si>
-  <si>
-    <t>짐을 정리하고 나오니 다른 마차가 새로 들어왔다.</t>
-  </si>
-  <si>
-    <t>아무래도 다른 곳에서도 파병을 온 모양이다.</t>
-  </si>
-  <si>
-    <t>마차에서는 3명의 어린 친구들이 내렸다. 소녀 2명과 소년 1명.</t>
-  </si>
-  <si>
-    <t>병사로써 온 사람이라고 보기에는 너무 어렸다. 학생 신분인가? 기사학교?</t>
-  </si>
-  <si>
-    <t>그런 생각을 하고 있었더니, 그 중 한명, 금발 소녀가 짐을 나르면서 나에게 인사했다.</t>
-  </si>
-  <si>
-    <t>Shian</t>
-  </si>
-  <si>
-    <t>LEFT</t>
+    <t>BattleScene</t>
+  </si>
+  <si>
+    <t>crawler</t>
+  </si>
+  <si>
+    <t>소녀의 움직임은 가히 눈부셨다.</t>
+  </si>
+  <si>
+    <t>빠르게 움직이는 번개처럼 그녀는 다인의 공격을 종이 한 장 차이로 피하며 연속적인 공격을 퍼부었다.</t>
+  </si>
+  <si>
+    <t>다인은 그녀의 움직임을 제대로 따라잡지도 못하고, 오히려 그 거대한 몸집이 느리게 느껴질 정도였다.</t>
+  </si>
+  <si>
+    <t>마지막 일격이 다인의 가슴 한가운데 정확히 꽂혔다.</t>
+  </si>
+  <si>
+    <t>녀석은 거대한 나무가 쓰러지듯 무너졌고, 지면이 크게 진동하며 흙먼지가 자욱하게 피어올랐다.</t>
+  </si>
+  <si>
+    <t>전투가 끝난 후 잠시 숨을 고른 소녀는 지친 기색도 없이 검을 재정비하며 일어섰다.</t>
+  </si>
+  <si>
+    <t>그녀의 전투 방식은 일반적인 전기 마법과 달랐다.</t>
+  </si>
+  <si>
+    <t>대부분의 전기 마법사는 원거리에서 스파크를 날려 공격하지만, 그녀는 마법으로 직접 신체 능력을 극한까지 끌어올려 검사로서의 전투를 수행했다.</t>
+  </si>
+  <si>
+    <t>극히 드물고 위험한 방법이지만, 그만큼 압도적인 힘을 보여주는 방식이었다.</t>
+  </si>
+  <si>
+    <t>그 모습은... 누군가의 전투 방식을 생각나게 하는 것이었다.</t>
+  </si>
+  <si>
+    <t>lubelia</t>
+  </si>
+  <si>
+    <t>RIGHT_CENTER</t>
+  </si>
+  <si>
+    <t>"후우... 시안! 말도 없이 혼자 뛰쳐나가면 어떡해요!"</t>
+  </si>
+  <si>
+    <t>내 뒤에서 앳된 목소리가 들렸다. 돌아보니 작은 체구의 갈색 머리 소녀가 숨을 헐떡이며 달려오고 있었다. 그녀는 방금 전 노란 머리 소녀, 시안보다 확실히 어려 보였다.</t>
+  </si>
+  <si>
+    <t>neria</t>
+  </si>
+  <si>
+    <t>"뭐어~ 루벨리아도 너무 열내지 말라니까"</t>
+  </si>
+  <si>
+    <t>그 뒤로 느긋한 어조의 하얀 머리 단발 소녀가 천천히 걸어왔다. 그녀는 시안과 또래 정도로 보였다.</t>
+  </si>
+  <si>
+    <t>"네리아가 그렇게 멋대로 좋게만 봐주니까, 시안이 자꾸 저렇게 제멋대로 행동하는 거예요. 진짜로 위험한 적이라도 만났으면 어쩌려고요!"</t>
+  </si>
+  <si>
+    <t>갈색 머리 소녀는 약간 틱틱대며 목소리를 높였다.</t>
+  </si>
+  <si>
+    <t>하지만 하얀머리 소녀, 네리아는 그녀의 말에 반응하지 않았다.</t>
+  </si>
+  <si>
+    <t>아무래도 담소를 나누고 있을만한 상황이 아니라는 것을 알아차린 듯 했다.</t>
+  </si>
+  <si>
+    <t>네리아</t>
+  </si>
+  <si>
+    <t>"……루벨리아."</t>
+  </si>
+  <si>
+    <t>루벨리아라고 불린 소녀는 그제야 주변의 끔찍한 광경을 눈치채고 말끝을 흐렸다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 주위에 널브러진 시체들을 보고 말문이 막힌 듯했다.</t>
+  </si>
+  <si>
+    <t>루벨리아</t>
+  </si>
+  <si>
+    <t>"…마차로 돌아가요."</t>
+  </si>
+  <si>
+    <t>짧게 내뱉고는 몸을 돌려 돌아가기 시작했다.</t>
+  </si>
+  <si>
+    <t>"시안~ 이제 가자구!"</t>
+  </si>
+  <si>
+    <t>네리아는 큰 소리로 다시 시안을 불렀다. 그러나 시안은 들은 척도 하지 않고, 다인의 시체 위에 가만히 앉아있을 뿐이었다.</t>
+  </si>
+  <si>
+    <t>"하아... 저 상태의 시안은 말려도 소용없단 말이지..."</t>
+  </si>
+  <si>
+    <t>네리아는 어깨를 으쓱하며 고개를 저었다. 그리고 곁에 있던 나를 발견한 듯 고개를 기울이며 물었다.</t>
+  </si>
+  <si>
+    <t>"어라? 병사님 혼자 살아남은 거예요?"</t>
+  </si>
+  <si>
+    <t>"...그렇게 됐네."</t>
+  </si>
+  <si>
+    <t>"헤에~ 어지간히 운도 안좋으신 병사님이시네요"</t>
+  </si>
+  <si>
+    <t>"그게 무슨 소리야."</t>
+  </si>
+  <si>
+    <t>"뭐어~ 살아남았다는게 꼭 좋은일은 아니니까요"</t>
+  </si>
+  <si>
+    <t>의미심장한 말을 남기고서 네리아는 느긋하게 몸을 돌려 루벨리아의 뒤를 따랐다.</t>
+  </si>
+  <si>
+    <t>CENTER</t>
+  </si>
+  <si>
+    <t>pureHeart</t>
+  </si>
+  <si>
+    <t>그녀들이 떠난 후, 시체더미 사이에서 홀로 서있는 시안의 모습을 바라보았다.</t>
+  </si>
+  <si>
+    <t>그녀는 고독하게, 말 없이 그 자리에 가만히 서 있었다.</t>
+  </si>
+  <si>
+    <t>무표정한 얼굴인 그녀는 말없이 허공을 응시하고 있었다.</t>
+  </si>
+  <si>
+    <t>그녀의 눈빛에서는 왠지 이루 말할 수 없는 무게감이 느껴지는 듯 했다.</t>
+  </si>
+  <si>
+    <t>"네 덕분에 살아남았어. 정말 고마워."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">깊게 생각하지 않고 그런 말을 뱉어버렸다. </t>
+  </si>
+  <si>
+    <t>그녀가 책임을 느끼는 듯한 표정을 보고있는 것이 마음에 들지 않아서 였을까</t>
+  </si>
+  <si>
+    <t>그 말을 들은 시안은 잠시 굳었던 표정을 풀고 억지로 밝은 미소를 지어 보였다.</t>
   </si>
   <si>
     <t>시안</t>
   </si>
   <si>
-    <t>"잘부탁드립니다~"</t>
-  </si>
-  <si>
-    <t>아 예. 잘 부탁드립니다. 하고 대답했다.</t>
-  </si>
-  <si>
-    <t>금발 소녀는 넉살이 좋은 성격인지 들어가면서 다른 사람들에게도 모두 인사했다.</t>
-  </si>
-  <si>
-    <t>다른 2명은 낯을 좀 가리는 모양인지 말없이 짐을 갖고 들어갔다.</t>
-  </si>
-  <si>
-    <t>서로 잘 모르는 사람들 끼리 어색한 인사를 나누고 있던 그 때 였다.</t>
-  </si>
-  <si>
-    <t>병영 안에서 보라색 머리의 큰 키를 한 여성이 나왔다.</t>
-  </si>
-  <si>
-    <t>세이라</t>
-  </si>
-  <si>
-    <t>"다들 먼 길 오느라 고생했네. 내가 케런베르크 경비대장인 세이라다"</t>
-  </si>
-  <si>
-    <t>경비대장 치고는 상당히 젊은 여성이었다.</t>
-  </si>
-  <si>
-    <t>"다들 정리가 끝나는대로 집합해서, 전원이 한 명씩 작은 시험을 볼거다. 다들 준비해서 나오도록 해"</t>
-  </si>
-  <si>
-    <t>그렇게 짧은 말을 던지고 세이라는 병영 안으로 다시 들어갔다.</t>
-  </si>
-  <si>
-    <t>시험... 인가</t>
-  </si>
-  <si>
-    <t>우리들의 전투력이 어느정도 되는지를 간단하게 보고자 하는 것 같았다.</t>
-  </si>
-  <si>
-    <t>보통 일반병은 대부분 전력이 되지 못한다.</t>
-  </si>
-  <si>
-    <t>제대로된 마법 기사 한명을 이기기 위해서는 몇십, 혹은 백에 가까운 일반병이 필요하기 때문이다.</t>
-  </si>
-  <si>
-    <t>인원 효율이 나지 않는다.</t>
-  </si>
-  <si>
-    <t>그럼에도 굳이 '전원' 모두 시험을 보겠다. 라고 하는건 어느정도 그녀의 가치관이 보이는 부분이기도 했다.</t>
-  </si>
-  <si>
-    <t>우리같은 일반병에게도 적절한 임무와 필요하면 전투까지 맡기겠다는 생각이다.</t>
-  </si>
-  <si>
-    <t>그것은 대장으로써 훌륭한 면모이기도 했지만 한 편으로는 마음에 들지 않아하는 사람도 있었다.</t>
-  </si>
-  <si>
-    <t>"아... 나는 전장에는 안나갈줄 알았는데, 검을 안뽑아 본지도 벌써 몇개월이야"</t>
-  </si>
-  <si>
-    <t>왕국 수도에서는 실제로 검을 쓸 일이 거의 없다.</t>
-  </si>
-  <si>
-    <t>사실상 우리같은 일반병은 그냥 왕국 내의 치안을 지키기 위해 존재할 뿐, 실제로 검을 뽑아 싸우게 될 일은 극히 드물다.</t>
-  </si>
-  <si>
-    <t>몇년동안 근무하면서 한 번도 검을 뽑아본 적이 없는 사람도 있다.</t>
-  </si>
-  <si>
-    <t>그러니까 그런 생각을 하는 사람들도 당연히 있었다.</t>
-  </si>
-  <si>
-    <t>물론 여긴 왕국 수도와는 다르다. 최전선에 왔으니 검을 뽑아야 하는 것은 당연한 일이다.</t>
-  </si>
-  <si>
-    <t>나도 마음을 다잡았다.</t>
-  </si>
-  <si>
-    <t>scene03</t>
-  </si>
-  <si>
-    <t>"으악!!"</t>
-  </si>
-  <si>
-    <t>비명소리가 들린다.</t>
-  </si>
-  <si>
-    <t>다음' 하는 소리가 들리고 곧이어 다시 또 다른 사람의 비명소리가 이어진다.</t>
-  </si>
-  <si>
-    <t>세이라 경비대장의 시험이 시작되어있었다.</t>
-  </si>
-  <si>
-    <t>신병 수는 우리 일반병사 약 30명에 기사학교 출신의 3명. 33명이다.</t>
-  </si>
-  <si>
-    <t>전원이 한명씩 경비대장과 직접 1대1로 전투를 치루어서 이루어지는 시험이다.</t>
-  </si>
-  <si>
-    <t>사실 33명이나 되는 수를 1대1로 모두 상대하는건 상당히 오랜 시간이 걸릴 것이라고 생각했다.</t>
-  </si>
-  <si>
-    <t>그야 여러가지 부분들을 봐야할테니까... 우리같은 일반 병사에게 마법을 쓰지는 않을테고...</t>
-  </si>
-  <si>
-    <t>그런 생각을 하고 있었지만, 오산이었던 것 같다.</t>
-  </si>
-  <si>
-    <t>세이라 경비대장은 거대한 대검을 사용했다.</t>
-  </si>
-  <si>
-    <t>단순히 봐도 저 몸집의 여성이 들기에는 굉장히 무거워보이는, 몸집보다도 거대한 대검이었다.</t>
-  </si>
-  <si>
-    <t>그녀는 그것을 마법 하나 사용하지 않고, 시험을 치르러 오는 일반병들을 차례차례 단 일격에 끝짱냈다.</t>
-  </si>
-  <si>
-    <t>표정은 썩 만족스러워 보이지는 않았다.</t>
-  </si>
-  <si>
-    <t>이것밖에 안되는 녀석들이 들어왔다니...</t>
-  </si>
-  <si>
-    <t>그녀의 표정에서는 그런 생각을 하고 있는것이 보일 정도였다.</t>
-  </si>
-  <si>
-    <t>넋놓고 그녀를 바라보고 있었더니 어느새 다음 차례가 찾아왔다.</t>
-  </si>
-  <si>
-    <t>"다음"</t>
-  </si>
-  <si>
-    <t>나는 그녀 앞에 조용히 다가가 섰다.</t>
-  </si>
-  <si>
-    <t>나름 검에 대해서 만큼은 자신이 있었다.</t>
-  </si>
-  <si>
-    <t>그리고 검을 뽑고, 그녀의 움직임에 집중했다.</t>
-  </si>
-  <si>
-    <t>"호오? 다른 녀석들이랑은 자세부터 다르네.. 이름을 먼저 물어볼까"</t>
-  </si>
-  <si>
-    <t>(이름 결정 씬)</t>
-  </si>
-  <si>
-    <t>"[] 입니다."</t>
-  </si>
-  <si>
-    <t>"[] 라... 한번 기대해보겠어!!"</t>
-  </si>
-  <si>
-    <t>(튜토리얼 전투씬)</t>
-  </si>
-  <si>
-    <t>나 또한 다른 병사들이랑 다를 것 없이 그녀의 일격에 영락없이 쓰러졌다.</t>
-  </si>
-  <si>
-    <t>그녀의 일격은 아주 묵직했다. 딱히 무언가 마법으로 강해진 모습이 아니었다.</t>
-  </si>
-  <si>
-    <t>순수하게 훈련을 통해 단련한 그녀의 힘.</t>
-  </si>
-  <si>
-    <t>잔머리를 굴려서 어떻게든 이겨보려 했으나, 전혀 통하지 않았다.</t>
-  </si>
-  <si>
-    <t>그녀는 상당히 강하다.</t>
-  </si>
-  <si>
-    <t>"너, 내 검을 피하려고 하지 않았지?"</t>
-  </si>
-  <si>
-    <t>그녀는 나에게 가까이 다가와서 쓰러진 나에게 쪼그리고 앉아서 말했다.</t>
-  </si>
-  <si>
-    <t>"맞으면 죽을거라고 생각하지 않았어?"</t>
-  </si>
-  <si>
-    <t>그야 맞으면 죽을거라 생각했지!!!</t>
-  </si>
-  <si>
-    <t>... 하지만 어느정도 내 생각을 그녀에게 말했다.</t>
-  </si>
-  <si>
-    <t>"... 대검은 크고 묵직한 만큼 연속적인 공격이 본래 힘들지만, 대장님의 공격은 그 움직임을 최소화해서 연속적인 공격으로 제 움직일 방향을 좁히는 형태였어요."</t>
-  </si>
-  <si>
-    <t>호? 그녀는 눈이 둥그레졌다.</t>
-  </si>
-  <si>
-    <t>"그래서 그 검을 한 번만 튕겨내거나, 각도라도 틀 수 있어도, 한 방 먹일 수 있을거라 생각했습니다."</t>
-  </si>
-  <si>
-    <t>그런데 생각보다 위력이 더 강력해서 전혀 힘쓸수 없었지만요. 하고 내가 웃었다.</t>
-  </si>
-  <si>
-    <t>세이라는 내 말을 듣더니 활짝 웃는 표정이 되었다.</t>
-  </si>
-  <si>
-    <t>"넌 합격이다. 매일 2층으로 정기출석하도록 해."</t>
-  </si>
-  <si>
-    <t>이만 물러가 하는 말에 나는 재빨리 일어나 자리를 피했다.</t>
-  </si>
-  <si>
-    <t>순간적으로 칭찬을 받았다는 기쁨과 동시에 괜한짓을 한 것 같다는 후회가 몰려왔다.</t>
-  </si>
-  <si>
-    <t>... 2층?</t>
-  </si>
-  <si>
-    <t>2층에 무엇이 있는것인지는 모르지만 분명한건 나에게 엄청난 임무를 맡길 것 같다는 느낌이었다.</t>
-  </si>
-  <si>
-    <t>아아... 어머니...</t>
-  </si>
-  <si>
-    <t>쥐 죽은 듯 조용히 살라는 어머니의 말씀을 이렇게 또 어기고 말았습니다...</t>
-  </si>
-  <si>
-    <t>저에게 군인은 아무래도 적성에 맞지 않는 모양이에요...</t>
-  </si>
-  <si>
-    <t>그런 생각을 하고 있다가 정신을 차리니 전투장이 시끌벅적했다.</t>
-  </si>
-  <si>
-    <t>아무래도 일반병 순서는 어느덧 끝나고, 기사학교 학생들의 차례가 된 듯 했다.</t>
-  </si>
-  <si>
-    <t>".... 이잇!!!"</t>
-  </si>
-  <si>
-    <t>아까전에 인사를 나눴던 넉살좋은 금발 소녀였다.</t>
-  </si>
-  <si>
-    <t>소녀는 재빠르게 움직이기 좋아 보이는, 그리 길지 않고 얇은 검 한 자루.</t>
-  </si>
-  <si>
-    <t>그 검으로 오히려 느린 세이라를 압박하기 위해 앞으로 나서서 검을 휘둘렀다.</t>
-  </si>
-  <si>
-    <t>그녀의 움직임은 아주 화려했다.</t>
-  </si>
-  <si>
-    <t>한 방 한 방이 강력하지는 않지만, 분명히 세이라를 조금씩 압박하고 있었다.</t>
-  </si>
-  <si>
-    <t>세이라는 그 순간 재빠른 그녀를 멀어지게 하기 위해 대검을 크게 휘둘렀다.</t>
-  </si>
-  <si>
-    <t>금발 소녀는 뒤로 크게 뛰며 멀어진다.</t>
-  </si>
-  <si>
-    <t>"여기까지야. 더 볼 필요가 없겠구나, 훌륭하군"</t>
-  </si>
-  <si>
-    <t>세이라 경비대장이 호쾌하게 웃었다.</t>
-  </si>
-  <si>
-    <t>확실히 마법을 전혀 사용하지 않고도 저 정도면 훌륭한 검사다.</t>
-  </si>
-  <si>
-    <t>"오늘은 여기까지야. 다들 수고 많았다. 결과는 정리해서 따로 전달해줄거다. 해산해도 좋아"</t>
-  </si>
-  <si>
-    <t>세이라의 늠름한 목소리가 장내에 퍼졌다.</t>
-  </si>
-  <si>
-    <t>다들 앉아서 구경하다가 일어나서 해산하기 시작했다.</t>
-  </si>
-  <si>
-    <t>나도 느릿하게 자리에서 일어나, 복귀하려고 할 때 였다.</t>
-  </si>
-  <si>
-    <t>"거기 []!"</t>
-  </si>
-  <si>
-    <t>세이라 대장이 나를 불러세웠다.</t>
-  </si>
-  <si>
-    <t>그 옆에는 방금전에 시험을 보고 있었던 금발 소녀도 같이 있었다.</t>
-  </si>
-  <si>
-    <t>"너희 둘은 내일부터 바로 같은조로 현장 투입이다."</t>
-  </si>
-  <si>
-    <t>으에!? 하는 멍청한 소리가 내 입으로 나오는 것을 최대한 참았다.</t>
-  </si>
-  <si>
-    <t>"저는 시안이에요. 아침에 봤었죠? 헤헤"</t>
-  </si>
-  <si>
-    <t>시안 이라고 소개한 소녀가 무해한 웃음을 지으며 말했다.</t>
-  </si>
-  <si>
-    <t>"내일... 바로 인가요..?"</t>
-  </si>
-  <si>
-    <t>"그래. 지금 전방에 나가있는 사람 수가 당장 부족해서 말이야.. 아직 공격이 들어오거나 하진 않았지만 너희 둘이 먼저 인원을 채워줬으면 좋겠다."</t>
-  </si>
-  <si>
-    <t>세이라는 골치라는 듯 머리를 잡으며 말했다.</t>
-  </si>
-  <si>
-    <t>"현장에 나가면 타일러 라는 녀석이 설명을 해줄거다. 나머지는 녀석에게 들으면 될 것 같아."</t>
-  </si>
-  <si>
-    <t>넵! 하고 시안이 대답하고, 세이라는 잘 부탁한다며 자리를 떠났다.</t>
-  </si>
-  <si>
-    <t>"[] 님이시죠? 내일부터 잘부탁해요~ 검 실력이 상당하시더라구요?"</t>
-  </si>
-  <si>
-    <t>나도 잘부탁해. 하고 인사를 나누고, 시안도 자리를 떠났다.</t>
-  </si>
-  <si>
-    <t>나는 잠시 멍해졌다.</t>
-  </si>
-  <si>
-    <t>아무리 그래도 이렇게나 빨리 전방까지 가게 되다니</t>
-  </si>
-  <si>
-    <t>어머니, 저는 어쩌면 좋을까요..?</t>
+    <t>"아하하, 고마워요 병사님. 제가 조금 더 일찍 알아챘다면 더 많은 사람을 구할 수 있었을 텐데... 그런 생각을 하고 있었어요."</t>
+  </si>
+  <si>
+    <t>"그러니까 그건——"</t>
+  </si>
+  <si>
+    <t>"책임이라든지, 누구 탓이라든지, 그런 이야기가 아니에요."</t>
+  </si>
+  <si>
+    <t>나는 순간 말문이 막혔다.</t>
+  </si>
+  <si>
+    <t>"그냥 구하고 싶었으니까요. 이 사람들을."</t>
+  </si>
+  <si>
+    <t>시안의 눈동자에는 깊은 슬픔과 결의가 뒤섞여 있었다.</t>
+  </si>
+  <si>
+    <t>그 눈빛 앞에서 나는 흔해빠진 위로의 말을 전하려는 것을 멈추었다.</t>
+  </si>
+  <si>
+    <t>그것에는 아무런 의미가 없었으니까.</t>
+  </si>
+  <si>
+    <t>그녀의 결의를 아름답다고 생각했다. 그것이 설령 일그러진 정의의 갈망이라 할지라도.</t>
+  </si>
+  <si>
+    <t>"이제 마차로 돌아가요. 병사님도 케런베르크로 가시는 거죠?"</t>
+  </si>
+  <si>
+    <t>"그래. 내가 얼마나 도움이 될지는 모르겠지만."</t>
+  </si>
+  <si>
+    <t>"하하, 그럴 리가요~ 병사님만이 할 수 있는 일이 분명히 있을 거예요. 분명 큰 도움이 되실 거라구요!"</t>
+  </si>
+  <si>
+    <t>"그래."</t>
+  </si>
+  <si>
+    <t>"앗, 그러고 보니 자기소개를 안 했네요!"</t>
+  </si>
+  <si>
+    <t>그녀는 갑자기 활기차게 내 앞으로 뛰어와 나를 올려다보았다.</t>
+  </si>
+  <si>
+    <t>"제 이름은 시안이에요. 아스트렐 왕국 13기사 중 한 명이었던 글라트가 제 아버지랍니다."</t>
+  </si>
+  <si>
+    <t>그녀가 내민 이름은 내가 가장 싫어하는 이름들 중 하나였다.</t>
+  </si>
+  <si>
+    <t>위선과 허상으로 점철된 이 왕국의 '정의'의 상징</t>
+  </si>
+  <si>
+    <t>그 이름에서부터 모든 게 시작된 것이었다.</t>
+  </si>
+  <si>
+    <t>이 모든 일그러진 운명의 시작이.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -568,6 +671,10 @@
       <sz val="11.0"/>
       <color rgb="FF303038"/>
       <name val="&quot;Malgun Gothic&quot;"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="3">
@@ -603,8 +710,8 @@
     <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf quotePrefix="1" borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -825,12 +932,12 @@
     <col customWidth="1" min="6" max="6" width="19.25"/>
     <col customWidth="1" min="7" max="7" width="16.0"/>
     <col customWidth="1" min="8" max="8" width="17.5"/>
-    <col customWidth="1" min="9" max="9" width="14.63"/>
-    <col customWidth="1" min="10" max="10" width="15.25"/>
-    <col customWidth="1" min="11" max="11" width="17.25"/>
-    <col customWidth="1" min="12" max="12" width="15.88"/>
-    <col customWidth="1" min="13" max="13" width="6.88"/>
-    <col customWidth="1" min="14" max="14" width="106.25"/>
+    <col customWidth="1" min="10" max="10" width="14.63"/>
+    <col customWidth="1" min="11" max="11" width="15.25"/>
+    <col customWidth="1" min="12" max="12" width="17.25"/>
+    <col customWidth="1" min="13" max="13" width="15.88"/>
+    <col customWidth="1" min="14" max="14" width="6.88"/>
+    <col customWidth="1" min="15" max="15" width="106.25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -864,10 +971,10 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
@@ -876,2162 +983,2677 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" s="2">
         <v>1.0</v>
       </c>
       <c r="C2" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>15</v>
+        <v>2.0</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K2" s="2">
+      <c r="L2" s="2">
         <v>0.5</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="O2" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" s="2">
         <v>2.0</v>
       </c>
       <c r="C3" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N3" s="3" t="s">
+        <v>0.3</v>
+      </c>
+      <c r="O3" s="3" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B4" s="2">
         <v>3.0</v>
       </c>
       <c r="C4" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N4" s="3" t="s">
+        <v>0.3</v>
+      </c>
+      <c r="O4" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5" s="2">
         <v>4.0</v>
       </c>
       <c r="C5" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N5" s="3" t="s">
+        <v>0.3</v>
+      </c>
+      <c r="O5" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" s="2">
         <v>5.0</v>
       </c>
       <c r="C6" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N6" s="3" t="s">
+        <v>0.3</v>
+      </c>
+      <c r="O6" s="3" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="2">
         <v>6.0</v>
       </c>
       <c r="C7" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N7" s="3" t="s">
+        <v>0.3</v>
+      </c>
+      <c r="O7" s="3" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8" s="2">
         <v>7.0</v>
       </c>
       <c r="C8" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N8" s="3" t="s">
+        <v>0.3</v>
+      </c>
+      <c r="O8" s="3" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B9" s="2">
         <v>8.0</v>
       </c>
       <c r="C9" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N9" s="3" t="s">
+        <v>0.3</v>
+      </c>
+      <c r="O9" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B10" s="2">
         <v>9.0</v>
       </c>
       <c r="C10" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N10" s="3" t="s">
+        <v>0.3</v>
+      </c>
+      <c r="O10" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B11" s="2">
         <v>10.0</v>
       </c>
       <c r="C11" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N11" s="3" t="s">
+        <v>0.3</v>
+      </c>
+      <c r="O11" s="3" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B12" s="2">
         <v>11.0</v>
       </c>
       <c r="C12" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N12" s="3" t="s">
+        <v>0.3</v>
+      </c>
+      <c r="O12" s="3" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B13" s="2">
         <v>12.0</v>
       </c>
       <c r="C13" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N13" s="3" t="s">
+        <v>0.3</v>
+      </c>
+      <c r="O13" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B14" s="2">
         <v>13.0</v>
       </c>
       <c r="C14" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N14" s="3" t="s">
+        <v>0.3</v>
+      </c>
+      <c r="O14" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B15" s="2">
         <v>14.0</v>
       </c>
       <c r="C15" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N15" s="3" t="s">
+        <v>0.3</v>
+      </c>
+      <c r="O15" s="3" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" s="2">
         <v>15.0</v>
       </c>
       <c r="C16" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N16" s="2" t="s">
+        <v>0.3</v>
+      </c>
+      <c r="O16" s="3" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B17" s="2">
         <v>16.0</v>
       </c>
       <c r="C17" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N17" s="3" t="s">
+        <v>0.3</v>
+      </c>
+      <c r="O17" s="3" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B18" s="2">
         <v>17.0</v>
       </c>
       <c r="C18" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N18" s="3" t="s">
+        <v>0.3</v>
+      </c>
+      <c r="O18" s="3" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B19" s="2">
         <v>18.0</v>
       </c>
       <c r="C19" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N19" s="3" t="s">
+        <v>0.3</v>
+      </c>
+      <c r="O19" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B20" s="2">
         <v>19.0</v>
       </c>
       <c r="C20" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N20" s="3" t="s">
+        <v>0.3</v>
+      </c>
+      <c r="O20" s="3" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B21" s="2">
         <v>20.0</v>
       </c>
       <c r="C21" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N21" s="3" t="s">
+        <v>0.3</v>
+      </c>
+      <c r="O21" s="3" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B22" s="2">
         <v>21.0</v>
       </c>
       <c r="C22" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N22" s="3" t="s">
+        <v>0.3</v>
+      </c>
+      <c r="O22" s="3" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B23" s="2">
         <v>22.0</v>
       </c>
       <c r="C23" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N23" s="3" t="s">
+        <v>0.3</v>
+      </c>
+      <c r="O23" s="3" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B24" s="2">
         <v>23.0</v>
       </c>
       <c r="C24" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N24" s="3" t="s">
+        <v>0.3</v>
+      </c>
+      <c r="O24" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B25" s="2">
         <v>24.0</v>
       </c>
       <c r="C25" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N25" s="3" t="s">
+        <v>0.3</v>
+      </c>
+      <c r="O25" s="3" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B26" s="2">
         <v>25.0</v>
       </c>
       <c r="C26" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N26" s="3" t="s">
+        <v>0.3</v>
+      </c>
+      <c r="O26" s="3" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B27" s="2">
         <v>26.0</v>
       </c>
       <c r="C27" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N27" s="2" t="s">
+        <v>0.3</v>
+      </c>
+      <c r="O27" s="3" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B28" s="2">
         <v>27.0</v>
       </c>
       <c r="C28" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N28" s="3" t="s">
+        <v>0.3</v>
+      </c>
+      <c r="O28" s="3" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B29" s="2">
         <v>28.0</v>
       </c>
       <c r="C29" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N29" s="3" t="s">
+        <v>0.3</v>
+      </c>
+      <c r="M29" s="2" t="s">
         <v>46</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B30" s="2">
         <v>29.0</v>
       </c>
       <c r="C30" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N30" s="3" t="s">
-        <v>47</v>
+        <v>0.3</v>
+      </c>
+      <c r="M30" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="O30" s="3" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B31" s="2">
         <v>30.0</v>
       </c>
       <c r="C31" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N31" s="3" t="s">
-        <v>48</v>
+        <v>0.3</v>
+      </c>
+      <c r="O31" s="3" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B32" s="2">
         <v>31.0</v>
       </c>
       <c r="C32" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>49</v>
+        <v>0.3</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B33" s="2">
         <v>32.0</v>
       </c>
       <c r="C33" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N33" s="3" t="s">
-        <v>50</v>
+        <v>0.3</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B34" s="2">
         <v>33.0</v>
       </c>
       <c r="C34" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N34" s="3" t="s">
-        <v>51</v>
+        <v>0.3</v>
+      </c>
+      <c r="O34" s="3" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B35" s="2">
         <v>34.0</v>
       </c>
       <c r="C35" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N35" s="3" t="s">
-        <v>52</v>
+        <v>0.3</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B36" s="2">
         <v>35.0</v>
       </c>
       <c r="C36" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N36" s="3" t="s">
-        <v>53</v>
+        <v>0.3</v>
+      </c>
+      <c r="O36" s="3" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B37" s="2">
         <v>36.0</v>
       </c>
       <c r="C37" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N37" s="3" t="s">
-        <v>54</v>
+        <v>0.3</v>
+      </c>
+      <c r="O37" s="3" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B38" s="2">
         <v>37.0</v>
       </c>
       <c r="C38" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>56</v>
+        <v>0.3</v>
+      </c>
+      <c r="O38" s="3" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="B39" s="2">
         <v>38.0</v>
       </c>
       <c r="C39" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="L39" s="2" t="s">
+        <v>0.3</v>
+      </c>
+      <c r="O39" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="N39" s="3" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="B40" s="2">
         <v>39.0</v>
       </c>
       <c r="C40" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N40" s="3" t="s">
-        <v>60</v>
+        <v>0.3</v>
+      </c>
+      <c r="O40" s="3" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="B41" s="2">
         <v>40.0</v>
       </c>
       <c r="C41" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N41" s="3" t="s">
-        <v>61</v>
+        <v>0.3</v>
+      </c>
+      <c r="O41" s="3" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="B42" s="2">
         <v>41.0</v>
       </c>
       <c r="C42" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N42" s="3" t="s">
-        <v>62</v>
+        <v>0.3</v>
+      </c>
+      <c r="O42" s="3" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="B43" s="2">
         <v>42.0</v>
       </c>
       <c r="C43" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N43" s="3" t="s">
-        <v>63</v>
+        <v>0.3</v>
+      </c>
+      <c r="O43" s="3" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="B44" s="2">
         <v>43.0</v>
       </c>
       <c r="C44" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="M44" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="N44" s="3" t="s">
-        <v>67</v>
+        <v>0.3</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="B45" s="2">
         <v>44.0</v>
       </c>
       <c r="C45" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>68</v>
+        <v>0.3</v>
+      </c>
+      <c r="O45" s="3" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="B46" s="2">
         <v>45.0</v>
       </c>
       <c r="C46" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N46" s="3" t="s">
-        <v>69</v>
+        <v>0.3</v>
+      </c>
+      <c r="O46" s="3" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="B47" s="2">
         <v>46.0</v>
       </c>
       <c r="C47" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>70</v>
+        <v>0.3</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="B48" s="2">
         <v>47.0</v>
       </c>
       <c r="C48" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N48" s="3" t="s">
-        <v>71</v>
+        <v>0.3</v>
+      </c>
+      <c r="O48" s="3" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="B49" s="2">
         <v>48.0</v>
       </c>
       <c r="C49" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N49" s="3" t="s">
-        <v>72</v>
+        <v>0.3</v>
+      </c>
+      <c r="O49" s="3" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="B50" s="2">
         <v>49.0</v>
       </c>
       <c r="C50" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="M50" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="N50" s="3" t="s">
-        <v>74</v>
+        <v>0.3</v>
+      </c>
+      <c r="O50" s="3" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="B51" s="2">
         <v>50.0</v>
       </c>
       <c r="C51" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N51" s="3" t="s">
-        <v>75</v>
+        <v>0.3</v>
+      </c>
+      <c r="O51" s="3" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="B52" s="2">
         <v>51.0</v>
       </c>
       <c r="C52" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="M52" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="N52" s="3" t="s">
-        <v>76</v>
+        <v>0.3</v>
+      </c>
+      <c r="O52" s="3" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="B53" s="2">
         <v>52.0</v>
       </c>
       <c r="C53" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N53" s="3" t="s">
-        <v>77</v>
+        <v>0.3</v>
+      </c>
+      <c r="O53" s="3" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="B54" s="2">
         <v>53.0</v>
       </c>
       <c r="C54" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N54" s="3" t="s">
-        <v>78</v>
+        <v>0.3</v>
+      </c>
+      <c r="O54" s="3" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="B55" s="2">
         <v>54.0</v>
       </c>
       <c r="C55" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N55" s="3" t="s">
-        <v>79</v>
+        <v>0.3</v>
+      </c>
+      <c r="O55" s="3" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="B56" s="2">
         <v>55.0</v>
       </c>
       <c r="C56" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N56" s="3" t="s">
-        <v>80</v>
+        <v>0.3</v>
+      </c>
+      <c r="O56" s="3" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="B57" s="2">
         <v>56.0</v>
       </c>
       <c r="C57" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N57" s="3" t="s">
-        <v>81</v>
+        <v>0.3</v>
+      </c>
+      <c r="M57" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="O57" s="3" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="B58" s="2">
         <v>57.0</v>
       </c>
       <c r="C58" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>82</v>
+        <v>0.3</v>
+      </c>
+      <c r="K58" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="L58" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="O58" s="3" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="B59" s="2">
         <v>58.0</v>
       </c>
       <c r="C59" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N59" s="3" t="s">
-        <v>83</v>
+        <v>0.3</v>
+      </c>
+      <c r="O59" s="3" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="B60" s="2">
         <v>59.0</v>
       </c>
       <c r="C60" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N60" s="3" t="s">
-        <v>84</v>
+        <v>0.3</v>
+      </c>
+      <c r="O60" s="3" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="B61" s="2">
         <v>60.0</v>
       </c>
       <c r="C61" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N61" s="3" t="s">
-        <v>85</v>
+        <v>0.3</v>
+      </c>
+      <c r="O61" s="3" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="B62" s="2">
         <v>61.0</v>
       </c>
       <c r="C62" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N62" s="3" t="s">
-        <v>86</v>
+        <v>0.3</v>
+      </c>
+      <c r="O62" s="3" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="B63" s="2">
         <v>62.0</v>
       </c>
       <c r="C63" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N63" s="3" t="s">
-        <v>87</v>
+        <v>0.3</v>
+      </c>
+      <c r="O63" s="3" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="B64" s="2">
         <v>63.0</v>
       </c>
       <c r="C64" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N64" s="3" t="s">
-        <v>88</v>
+        <v>0.3</v>
+      </c>
+      <c r="M64" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="O64" s="3" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="B65" s="2">
         <v>64.0</v>
       </c>
       <c r="C65" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N65" s="3" t="s">
-        <v>89</v>
+        <v>0.3</v>
+      </c>
+      <c r="O65" s="3" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="B66" s="2">
         <v>65.0</v>
       </c>
       <c r="C66" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N66" s="3" t="s">
-        <v>90</v>
+        <v>0.3</v>
+      </c>
+      <c r="O66" s="3" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="B67" s="2">
         <v>66.0</v>
       </c>
       <c r="C67" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N67" s="3" t="s">
-        <v>91</v>
+        <v>0.3</v>
+      </c>
+      <c r="N67" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="O67" s="3" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="B68" s="2">
         <v>67.0</v>
       </c>
       <c r="C68" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N68" s="3" t="s">
-        <v>92</v>
+        <v>0.3</v>
+      </c>
+      <c r="O68" s="3" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B69" s="2">
         <v>68.0</v>
       </c>
       <c r="C69" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N69" s="3" t="s">
-        <v>94</v>
+        <v>0.3</v>
+      </c>
+      <c r="O69" s="3" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B70" s="2">
         <v>69.0</v>
       </c>
       <c r="C70" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N70" s="3" t="s">
-        <v>95</v>
+        <v>0.3</v>
+      </c>
+      <c r="O70" s="3" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B71" s="2">
         <v>70.0</v>
       </c>
       <c r="C71" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N71" s="4" t="s">
-        <v>96</v>
+        <v>0.3</v>
+      </c>
+      <c r="O71" s="3" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B72" s="2">
         <v>71.0</v>
       </c>
       <c r="C72" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N72" s="3" t="s">
-        <v>97</v>
+        <v>0.3</v>
+      </c>
+      <c r="N72" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="O72" s="3" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B73" s="2">
         <v>72.0</v>
       </c>
       <c r="C73" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N73" s="3" t="s">
-        <v>98</v>
+        <v>0.3</v>
+      </c>
+      <c r="O73" s="3" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B74" s="2">
         <v>73.0</v>
       </c>
       <c r="C74" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N74" s="3" t="s">
-        <v>99</v>
+        <v>0.3</v>
+      </c>
+      <c r="O74" s="3" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B75" s="2">
         <v>74.0</v>
       </c>
       <c r="C75" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N75" s="3" t="s">
-        <v>100</v>
+        <v>0.3</v>
+      </c>
+      <c r="O75" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B76" s="2">
         <v>75.0</v>
       </c>
       <c r="C76" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N76" s="3" t="s">
-        <v>101</v>
+        <v>0.3</v>
+      </c>
+      <c r="O76" s="3" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B77" s="2">
         <v>76.0</v>
       </c>
       <c r="C77" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N77" s="3" t="s">
-        <v>102</v>
+        <v>0.3</v>
+      </c>
+      <c r="O77" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B78" s="2">
         <v>77.0</v>
       </c>
       <c r="C78" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N78" s="3" t="s">
-        <v>103</v>
+        <v>0.3</v>
+      </c>
+      <c r="O78" s="3" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B79" s="2">
         <v>78.0</v>
       </c>
       <c r="C79" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N79" s="3" t="s">
-        <v>104</v>
+        <v>0.3</v>
+      </c>
+      <c r="O79" s="3" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B80" s="2">
         <v>79.0</v>
       </c>
       <c r="C80" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N80" s="3" t="s">
-        <v>105</v>
+        <v>0.3</v>
+      </c>
+      <c r="O80" s="3" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B81" s="2">
         <v>80.0</v>
       </c>
       <c r="C81" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N81" s="3" t="s">
-        <v>106</v>
+        <v>0.3</v>
+      </c>
+      <c r="O81" s="3" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B82" s="2">
         <v>81.0</v>
       </c>
       <c r="C82" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N82" s="3" t="s">
-        <v>107</v>
+        <v>0.3</v>
+      </c>
+      <c r="O82" s="3" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B83" s="2">
         <v>82.0</v>
       </c>
       <c r="C83" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N83" s="3" t="s">
-        <v>108</v>
+        <v>0.3</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B84" s="2">
         <v>83.0</v>
       </c>
       <c r="C84" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N84" s="3" t="s">
-        <v>109</v>
+        <v>0.3</v>
+      </c>
+      <c r="O84" s="3" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B85" s="2">
         <v>84.0</v>
       </c>
       <c r="C85" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N85" s="3" t="s">
-        <v>110</v>
+        <v>0.3</v>
+      </c>
+      <c r="O85" s="3" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B86" s="2">
         <v>85.0</v>
       </c>
       <c r="C86" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N86" s="3" t="s">
-        <v>111</v>
+        <v>0.3</v>
+      </c>
+      <c r="O86" s="3" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B87" s="2">
         <v>86.0</v>
       </c>
       <c r="C87" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N87" s="3" t="s">
-        <v>112</v>
+        <v>0.3</v>
+      </c>
+      <c r="O87" s="3" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B88" s="2">
         <v>87.0</v>
       </c>
       <c r="C88" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N88" s="3" t="s">
-        <v>113</v>
+        <v>0.3</v>
+      </c>
+      <c r="O88" s="3" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B89" s="2">
         <v>88.0</v>
       </c>
       <c r="C89" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N89" s="3" t="s">
-        <v>114</v>
+        <v>0.3</v>
+      </c>
+      <c r="O89" s="3" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B90" s="2">
         <v>89.0</v>
       </c>
       <c r="C90" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N90" s="3" t="s">
-        <v>115</v>
+        <v>0.3</v>
+      </c>
+      <c r="H90" s="4"/>
+      <c r="M90" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="O90" s="3" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B91" s="2">
         <v>90.0</v>
       </c>
       <c r="C91" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>116</v>
+        <v>0.3</v>
+      </c>
+      <c r="H91" s="4"/>
+      <c r="K91" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="L91" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="M91" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="O91" s="3" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B92" s="2">
         <v>91.0</v>
       </c>
       <c r="C92" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N92" s="3" t="s">
-        <v>117</v>
+        <v>0.3</v>
+      </c>
+      <c r="O92" s="3" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B93" s="2">
         <v>92.0</v>
       </c>
       <c r="C93" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N93" s="3" t="s">
-        <v>118</v>
+        <v>0.3</v>
+      </c>
+      <c r="O93" s="3" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B94" s="2">
         <v>93.0</v>
       </c>
       <c r="C94" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>94</v>
+        <v>0.3</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B95" s="2">
         <v>94.0</v>
       </c>
       <c r="C95" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N95" s="3" t="s">
+        <v>0.3</v>
+      </c>
+      <c r="O95" s="3" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B96" s="2">
         <v>95.0</v>
       </c>
       <c r="C96" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N96" s="3" t="s">
+        <v>0.3</v>
+      </c>
+      <c r="O96" s="3" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B97" s="2">
         <v>96.0</v>
       </c>
       <c r="C97" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N97" s="3" t="s">
+        <v>0.3</v>
+      </c>
+      <c r="O97" s="3" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B98" s="2">
         <v>97.0</v>
       </c>
       <c r="C98" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N98" s="3" t="s">
+        <v>0.3</v>
+      </c>
+      <c r="O98" s="3" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B99" s="2">
         <v>98.0</v>
       </c>
       <c r="C99" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N99" s="3" t="s">
+        <v>0.3</v>
+      </c>
+      <c r="D99" s="2" t="s">
         <v>123</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N99" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="O99" s="3" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B100" s="2">
         <v>99.0</v>
       </c>
       <c r="C100" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>124</v>
+        <v>0.3</v>
+      </c>
+      <c r="O100" s="3" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B101" s="2">
         <v>100.0</v>
       </c>
       <c r="C101" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N101" s="3" t="s">
-        <v>125</v>
+        <v>0.3</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B102" s="2">
         <v>101.0</v>
       </c>
       <c r="C102" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N102" s="3" t="s">
-        <v>126</v>
+        <v>0.3</v>
+      </c>
+      <c r="N102" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="O102" s="3" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B103" s="2">
         <v>102.0</v>
       </c>
       <c r="C103" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N103" s="3" t="s">
-        <v>127</v>
+        <v>0.3</v>
+      </c>
+      <c r="O103" s="3" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B104" s="2">
         <v>103.0</v>
       </c>
       <c r="C104" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N104" s="3" t="s">
-        <v>128</v>
+        <v>0.3</v>
+      </c>
+      <c r="O104" s="3" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B105" s="2">
         <v>104.0</v>
       </c>
       <c r="C105" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N105" s="3" t="s">
-        <v>129</v>
+        <v>0.3</v>
+      </c>
+      <c r="O105" s="3" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B106" s="2">
         <v>105.0</v>
       </c>
       <c r="C106" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N106" s="3" t="s">
-        <v>130</v>
+        <v>0.3</v>
+      </c>
+      <c r="O106" s="3" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B107" s="2">
         <v>106.0</v>
       </c>
       <c r="C107" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N107" s="3" t="s">
-        <v>131</v>
+        <v>0.3</v>
+      </c>
+      <c r="N107" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="O107" s="3" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B108" s="2">
         <v>107.0</v>
       </c>
       <c r="C108" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N108" s="3" t="s">
-        <v>132</v>
-      </c>
+        <v>3.0</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="I108" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="O108" s="3"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B109" s="2">
         <v>108.0</v>
       </c>
       <c r="C109" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N109" s="3" t="s">
-        <v>133</v>
+        <v>0.3</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K109" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="L109" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="M109" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="O109" s="3" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B110" s="2">
         <v>109.0</v>
       </c>
       <c r="C110" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N110" s="3" t="s">
-        <v>134</v>
+        <v>0.3</v>
+      </c>
+      <c r="O110" s="3" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B111" s="2">
         <v>110.0</v>
       </c>
       <c r="C111" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N111" s="3" t="s">
-        <v>135</v>
+        <v>0.3</v>
+      </c>
+      <c r="O111" s="3" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B112" s="2">
         <v>111.0</v>
       </c>
       <c r="C112" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N112" s="3" t="s">
-        <v>136</v>
+        <v>0.3</v>
+      </c>
+      <c r="O112" s="3" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B113" s="2">
         <v>112.0</v>
       </c>
       <c r="C113" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N113" s="3" t="s">
-        <v>137</v>
+        <v>0.3</v>
+      </c>
+      <c r="O113" s="3" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B114" s="2">
         <v>113.0</v>
       </c>
       <c r="C114" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N114" s="3" t="s">
-        <v>138</v>
+        <v>0.3</v>
+      </c>
+      <c r="O114" s="3" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B115" s="2">
         <v>114.0</v>
       </c>
       <c r="C115" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N115" s="3" t="s">
-        <v>139</v>
+        <v>0.3</v>
+      </c>
+      <c r="O115" s="3" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B116" s="2">
         <v>115.0</v>
       </c>
       <c r="C116" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N116" s="3" t="s">
-        <v>140</v>
+        <v>0.3</v>
+      </c>
+      <c r="O116" s="3" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B117" s="2">
         <v>116.0</v>
       </c>
       <c r="C117" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N117" s="3" t="s">
-        <v>141</v>
+        <v>0.3</v>
+      </c>
+      <c r="O117" s="3" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B118" s="2">
         <v>117.0</v>
       </c>
       <c r="C118" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N118" s="3" t="s">
-        <v>142</v>
+        <v>0.3</v>
+      </c>
+      <c r="O118" s="3" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B119" s="2">
         <v>118.0</v>
       </c>
       <c r="C119" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N119" s="3" t="s">
-        <v>143</v>
+        <v>0.3</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F119" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N119" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="O119" s="3" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B120" s="2">
         <v>119.0</v>
       </c>
       <c r="C120" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N120" s="3" t="s">
-        <v>144</v>
+        <v>0.3</v>
+      </c>
+      <c r="O120" s="3" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B121" s="2">
         <v>120.0</v>
       </c>
       <c r="C121" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N121" s="3" t="s">
-        <v>145</v>
+        <v>0.3</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N121" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="O121" s="3" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B122" s="2">
         <v>121.0</v>
       </c>
       <c r="C122" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N122" s="3" t="s">
-        <v>146</v>
+        <v>0.3</v>
+      </c>
+      <c r="O122" s="3" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B123" s="2">
         <v>122.0</v>
       </c>
       <c r="C123" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N123" s="3" t="s">
-        <v>147</v>
+        <v>0.3</v>
+      </c>
+      <c r="N123" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="O123" s="3" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B124" s="2">
         <v>123.0</v>
       </c>
       <c r="C124" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N124" s="3" t="s">
-        <v>148</v>
+        <v>0.3</v>
+      </c>
+      <c r="O124" s="3" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B125" s="2">
         <v>124.0</v>
       </c>
       <c r="C125" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N125" s="3" t="s">
-        <v>149</v>
+        <v>0.3</v>
+      </c>
+      <c r="N125" s="2"/>
+      <c r="O125" s="3" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B126" s="2">
         <v>125.0</v>
       </c>
       <c r="C126" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N126" s="3" t="s">
-        <v>150</v>
+        <v>0.3</v>
+      </c>
+      <c r="N126" s="2"/>
+      <c r="O126" s="3" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B127" s="2">
         <v>126.0</v>
       </c>
       <c r="C127" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N127" s="3" t="s">
-        <v>151</v>
+        <v>0.3</v>
+      </c>
+      <c r="N127" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="O127" s="3" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B128" s="2">
         <v>127.0</v>
       </c>
       <c r="C128" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N128" s="3" t="s">
-        <v>152</v>
+        <v>0.3</v>
+      </c>
+      <c r="O128" s="3" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B129" s="2">
         <v>128.0</v>
       </c>
       <c r="C129" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N129" s="3" t="s">
-        <v>153</v>
+        <v>0.3</v>
+      </c>
+      <c r="N129" s="2"/>
+      <c r="O129" s="3" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B130" s="2">
         <v>129.0</v>
       </c>
       <c r="C130" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N130" s="3" t="s">
-        <v>154</v>
+        <v>0.3</v>
+      </c>
+      <c r="N130" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="O130" s="3" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B131" s="2">
         <v>130.0</v>
       </c>
       <c r="C131" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N131" s="3" t="s">
-        <v>155</v>
+        <v>0.3</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F131" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="O131" s="3" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B132" s="2">
         <v>131.0</v>
       </c>
       <c r="C132" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N132" s="3" t="s">
-        <v>156</v>
+        <v>0.3</v>
+      </c>
+      <c r="N132" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="O132" s="3" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B133" s="2">
         <v>132.0</v>
       </c>
       <c r="C133" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N133" s="3" t="s">
-        <v>157</v>
+        <v>0.3</v>
+      </c>
+      <c r="O133" s="3" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B134" s="2">
         <v>133.0</v>
       </c>
       <c r="C134" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N134" s="3" t="s">
-        <v>158</v>
+        <v>0.3</v>
+      </c>
+      <c r="N134" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="O134" s="3" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B135" s="2">
         <v>134.0</v>
       </c>
       <c r="C135" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N135" s="3" t="s">
-        <v>159</v>
+        <v>0.3</v>
+      </c>
+      <c r="O135" s="3" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B136" s="2">
         <v>135.0</v>
       </c>
       <c r="C136" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N136" s="3" t="s">
-        <v>160</v>
+        <v>0.3</v>
+      </c>
+      <c r="N136" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="O136" s="3" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B137" s="2">
         <v>136.0</v>
       </c>
       <c r="C137" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N137" s="3" t="s">
-        <v>161</v>
+        <v>0.3</v>
+      </c>
+      <c r="N137" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="O137" s="3" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B138" s="2">
         <v>137.0</v>
       </c>
       <c r="C138" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N138" s="3" t="s">
+        <v>0.3</v>
+      </c>
+      <c r="N138" s="2" t="s">
         <v>162</v>
+      </c>
+      <c r="O138" s="3" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B139" s="2">
         <v>138.0</v>
       </c>
       <c r="C139" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N139" s="3" t="s">
-        <v>163</v>
+        <v>0.3</v>
+      </c>
+      <c r="N139" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="O139" s="3" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B140" s="2">
         <v>139.0</v>
       </c>
       <c r="C140" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N140" s="3" t="s">
-        <v>164</v>
+        <v>0.3</v>
+      </c>
+      <c r="N140" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="O140" s="3" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B141" s="2">
         <v>140.0</v>
       </c>
       <c r="C141" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N141" s="3" t="s">
-        <v>165</v>
+        <v>0.3</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="F141" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="O141" s="3" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B142" s="2">
         <v>141.0</v>
       </c>
       <c r="C142" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N142" s="3" t="s">
-        <v>166</v>
+        <v>0.3</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="F142" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="K142" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="L142" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="O142" s="3" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B143" s="2">
         <v>142.0</v>
       </c>
       <c r="C143" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N143" s="3" t="s">
-        <v>167</v>
+        <v>0.3</v>
+      </c>
+      <c r="D143" s="2"/>
+      <c r="E143" s="2"/>
+      <c r="F143" s="2"/>
+      <c r="O143" s="3" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B144" s="2">
         <v>143.0</v>
       </c>
       <c r="C144" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N144" s="3" t="s">
-        <v>168</v>
+        <v>0.3</v>
+      </c>
+      <c r="D144" s="2"/>
+      <c r="E144" s="2"/>
+      <c r="F144" s="2"/>
+      <c r="O144" s="3" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B145" s="2">
         <v>144.0</v>
       </c>
       <c r="C145" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N145" s="3" t="s">
-        <v>169</v>
+        <v>0.3</v>
+      </c>
+      <c r="N145" s="2"/>
+      <c r="O145" s="3" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B146" s="2">
         <v>145.0</v>
       </c>
       <c r="C146" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N146" s="3" t="s">
-        <v>170</v>
+        <v>0.3</v>
+      </c>
+      <c r="N146" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="O146" s="3" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B147" s="2">
         <v>146.0</v>
       </c>
       <c r="C147" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N147" s="3" t="s">
-        <v>171</v>
+        <v>0.3</v>
+      </c>
+      <c r="O147" s="3" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B148" s="2">
         <v>147.0</v>
       </c>
       <c r="C148" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N148" s="3" t="s">
-        <v>172</v>
+        <v>0.3</v>
+      </c>
+      <c r="O148" s="3" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B149" s="2">
         <v>148.0</v>
       </c>
       <c r="C149" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N149" s="3" t="s">
-        <v>173</v>
+        <v>0.3</v>
+      </c>
+      <c r="O149" s="3" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B150" s="2">
         <v>149.0</v>
       </c>
       <c r="C150" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N150" s="3" t="s">
-        <v>174</v>
+        <v>0.3</v>
+      </c>
+      <c r="N150" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="O150" s="3" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B151" s="2">
         <v>150.0</v>
       </c>
       <c r="C151" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N151" s="3" t="s">
-        <v>175</v>
-      </c>
+        <v>0.3</v>
+      </c>
+      <c r="N151" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="O151" s="3" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" s="2">
+        <v>151.0</v>
+      </c>
+      <c r="C152" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="N152" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="O152" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B153" s="2">
+        <v>152.0</v>
+      </c>
+      <c r="C153" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="O153" s="3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B154" s="2">
+        <v>153.0</v>
+      </c>
+      <c r="C154" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="N154" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="O154" s="3" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B155" s="2">
+        <v>154.0</v>
+      </c>
+      <c r="C155" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="O155" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B156" s="2">
+        <v>155.0</v>
+      </c>
+      <c r="C156" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="O156" s="3" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B157" s="2">
+        <v>156.0</v>
+      </c>
+      <c r="C157" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="O157" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B158" s="2">
+        <v>157.0</v>
+      </c>
+      <c r="C158" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="O158" s="3" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B159" s="2">
+        <v>158.0</v>
+      </c>
+      <c r="C159" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="N159" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="O159" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B160" s="2">
+        <v>159.0</v>
+      </c>
+      <c r="C160" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="N160" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="O160" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B161" s="2">
+        <v>160.0</v>
+      </c>
+      <c r="C161" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="N161" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="O161" s="3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B162" s="2">
+        <v>161.0</v>
+      </c>
+      <c r="C162" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="N162" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="O162" s="3" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B163" s="2">
+        <v>162.0</v>
+      </c>
+      <c r="C163" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="N163" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="O163" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B164" s="2">
+        <v>163.0</v>
+      </c>
+      <c r="C164" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="O164" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B165" s="2">
+        <v>164.0</v>
+      </c>
+      <c r="C165" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="N165" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="O165" s="3" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B166" s="2">
+        <v>165.0</v>
+      </c>
+      <c r="C166" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="O166" s="3" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B167" s="2">
+        <v>166.0</v>
+      </c>
+      <c r="C167" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="F167" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="M167" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="O167" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B168" s="2">
+        <v>167.0</v>
+      </c>
+      <c r="C168" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="O168" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B169" s="2">
+        <v>168.0</v>
+      </c>
+      <c r="C169" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="O169" s="3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="O170" s="3"/>
+    </row>
+    <row r="171">
+      <c r="O171" s="3"/>
+    </row>
+    <row r="172">
+      <c r="O172" s="3"/>
+    </row>
+    <row r="173">
+      <c r="O173" s="3"/>
+    </row>
+    <row r="174">
+      <c r="O174" s="3"/>
+    </row>
+    <row r="175">
+      <c r="O175" s="3"/>
+    </row>
+    <row r="176">
+      <c r="O176" s="3"/>
+    </row>
+    <row r="177">
+      <c r="O177" s="3"/>
+    </row>
+    <row r="178">
+      <c r="O178" s="3"/>
+    </row>
+    <row r="179">
+      <c r="O179" s="3"/>
+    </row>
+    <row r="180">
+      <c r="O180" s="3"/>
+    </row>
+    <row r="181">
+      <c r="O181" s="3"/>
+    </row>
+    <row r="182">
+      <c r="O182" s="3"/>
+    </row>
+    <row r="183">
+      <c r="O183" s="3"/>
+    </row>
+    <row r="184">
+      <c r="O184" s="3"/>
+    </row>
+    <row r="185">
+      <c r="O185" s="3"/>
+    </row>
+    <row r="186">
+      <c r="O186" s="3"/>
+    </row>
+    <row r="187">
+      <c r="O187" s="3"/>
+    </row>
+    <row r="188">
+      <c r="O188" s="3"/>
+    </row>
+    <row r="189">
+      <c r="O189" s="3"/>
+    </row>
+    <row r="190">
+      <c r="O190" s="3"/>
+    </row>
+    <row r="191">
+      <c r="O191" s="3"/>
+    </row>
+    <row r="192">
+      <c r="O192" s="3"/>
+    </row>
+    <row r="193">
+      <c r="O193" s="3"/>
+    </row>
+    <row r="194">
+      <c r="O194" s="3"/>
+    </row>
+    <row r="195">
+      <c r="O195" s="3"/>
     </row>
   </sheetData>
+  <autoFilter ref="$O$2:$O$195"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>